--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1967F0A-FF15-48B9-94C2-96046FFC6096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3D5F6B-B80C-4B03-A2CD-6F288D398897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,12 +170,6 @@
 Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896—97, combinés avec les statistiques des naissances. La différence première obtenue l0 − Σdx est distribuée par tous les groupes d’âge (sexe masculin 14 494, sexe féminin 12 884).</t>
   </si>
   <si>
-    <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1896/97 г. и данным о родившихся за 1775—1897 гг.
-Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
-Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).
-Техническое замечание: строки возрастов 49–50 отсутствуют на скане между PDF-страницами 159 и 160; соответствующие значения восстановлены по смежным lₓ/Tₓ/Lₓ и табличным тождествам.</t>
-  </si>
-  <si>
     <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1907—1910 гг. и данным о родившихся за 1785—1910 гг.
 Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 13 319, для женщин 14 805, распределена пропорционально на возрастные группы, начиная с 15 лет.
 Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1907—1910, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 13 319, sexe féminin 14 805).</t>
@@ -215,6 +209,12 @@
   </si>
   <si>
     <t xml:space="preserve">50 губерний Европейской России. 1874—1883 </t>
+  </si>
+  <si>
+    <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1896/97 г. и данным о родившихся за 1775—1897 гг.
+Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
+Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).
+Техническое замечание: строки возрастов 49–50 отсутствуют на скане между PDF-страницами 159 и 160; соответствующие значения восстановлены по смежным lₓ/Tₓ/Lₓ и табличным тождествам.</t>
   </si>
 </sst>
 </file>
@@ -507,18 +507,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -527,6 +515,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -567,19 +570,16 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -758,12 +758,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2"/>
@@ -772,12 +772,12 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
@@ -832,12 +832,12 @@
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
@@ -858,13 +858,13 @@
         <v>41</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
@@ -878,7 +878,7 @@
         <v>33</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
@@ -895,18 +895,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" ht="158.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
@@ -920,7 +920,7 @@
         <v>37</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -952,71 +952,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A1" s="55" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
+      <c r="A1" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="23"/>
-      <c r="K4" s="59" t="s">
+      <c r="K4" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="59"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
-      <c r="Q4" s="59"/>
-      <c r="R4" s="59"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
     </row>
     <row r="5" spans="1:18" ht="26.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="33" t="s">
@@ -6500,7 +6500,7 @@
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -6552,48 +6552,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
+      <c r="A1" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="44"/>
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4"/>
@@ -6617,27 +6617,27 @@
     </row>
     <row r="4" spans="1:18" ht="10.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
       <c r="J4" s="21"/>
-      <c r="K4" s="45" t="s">
+      <c r="K4" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
     </row>
     <row r="5" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
@@ -12148,26 +12148,26 @@
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="B108" s="47"/>
-      <c r="C108" s="47"/>
-      <c r="D108" s="47"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="47"/>
-      <c r="G108" s="47"/>
-      <c r="H108" s="47"/>
-      <c r="I108" s="47"/>
-      <c r="J108" s="47"/>
-      <c r="K108" s="47"/>
-      <c r="L108" s="47"/>
-      <c r="M108" s="47"/>
-      <c r="N108" s="47"/>
-      <c r="O108" s="47"/>
-      <c r="P108" s="47"/>
-      <c r="Q108" s="47"/>
-      <c r="R108" s="47"/>
+      <c r="A108" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108" s="48"/>
+      <c r="C108" s="48"/>
+      <c r="D108" s="48"/>
+      <c r="E108" s="48"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="48"/>
+      <c r="H108" s="48"/>
+      <c r="I108" s="48"/>
+      <c r="J108" s="48"/>
+      <c r="K108" s="48"/>
+      <c r="L108" s="48"/>
+      <c r="M108" s="48"/>
+      <c r="N108" s="48"/>
+      <c r="O108" s="48"/>
+      <c r="P108" s="48"/>
+      <c r="Q108" s="48"/>
+      <c r="R108" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12198,48 +12198,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
+      <c r="A1" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5"/>
@@ -12263,53 +12263,53 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="22"/>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="52" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="51" t="s">
+      <c r="K4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="51" t="s">
+      <c r="L4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="51" t="s">
+      <c r="M4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="51" t="s">
+      <c r="N4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="O4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="51" t="s">
+      <c r="P4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="51" t="s">
+      <c r="Q4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="51" t="s">
+      <c r="R4" s="52" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17851,98 +17851,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
+      <c r="A1" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="22"/>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="55" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="54" t="s">
+      <c r="L4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="54" t="s">
+      <c r="M4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="54" t="s">
+      <c r="N4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="54" t="s">
+      <c r="P4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="54" t="s">
+      <c r="Q4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="54" t="s">
+      <c r="R4" s="55" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23476,70 +23476,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
+      <c r="A1" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="59"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="K4" s="36" t="s">
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="K4" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
     </row>
     <row r="5" spans="1:18" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="32" t="s">

--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3D5F6B-B80C-4B03-A2CD-6F288D398897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021DA8FF-8B98-406F-B215-D9FB89655593}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -749,15 +749,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="50.41796875" customWidth="1"/>
-    <col min="3" max="3" width="30.26171875" customWidth="1"/>
+    <col min="2" max="2" width="50.375" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
     <col min="4" max="4" width="115" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -765,13 +765,13 @@
       <c r="C1" s="36"/>
       <c r="D1" s="36"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" ht="17.45" customHeight="1">
       <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
@@ -779,7 +779,7 @@
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
     </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -789,7 +789,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" ht="28.5">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -799,7 +799,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" ht="42.75">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -809,7 +809,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -819,19 +819,19 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4">
       <c r="A10" s="37" t="s">
         <v>10</v>
       </c>
@@ -839,7 +839,7 @@
       <c r="C10" s="36"/>
       <c r="D10" s="36"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" ht="15">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -853,7 +853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" ht="114">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -867,7 +867,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" ht="99.75">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -881,7 +881,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" ht="114">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -895,7 +895,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="158.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" ht="156.75">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" ht="114">
       <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
@@ -936,9 +936,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.5234375" customWidth="1"/>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
@@ -951,7 +951,7 @@
     <col min="17" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:18" ht="15.75">
       <c r="A1" s="38" t="s">
         <v>50</v>
       </c>
@@ -973,7 +973,7 @@
       <c r="Q1" s="39"/>
       <c r="R1" s="39"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="40" t="s">
         <v>31</v>
       </c>
@@ -995,7 +995,7 @@
       <c r="Q2" s="40"/>
       <c r="R2" s="40"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="15">
       <c r="B4" s="41" t="s">
         <v>16</v>
       </c>
@@ -1018,7 +1018,7 @@
       <c r="Q4" s="42"/>
       <c r="R4" s="42"/>
     </row>
-    <row r="5" spans="1:18" ht="26.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="26.45" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>18</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18">
       <c r="A6" s="19">
         <v>0</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>14.52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18">
       <c r="A7" s="19">
         <v>1</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>45.42</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18">
       <c r="A8" s="19">
         <v>2</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>49.91</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18">
       <c r="A9" s="19">
         <v>3</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18">
       <c r="A10" s="19">
         <v>4</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>51.82</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18">
       <c r="A11" s="19">
         <v>5</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>51.79</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18">
       <c r="A12" s="19">
         <v>6</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18">
       <c r="A13" s="19">
         <v>7</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18">
       <c r="A14" s="19">
         <v>8</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18">
       <c r="A15" s="19">
         <v>9</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>49.43</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18">
       <c r="A16" s="19">
         <v>10</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>48.62</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="19">
         <v>11</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>47.78</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="19">
         <v>12</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>46.93</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="19">
         <v>13</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>46.06</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="19">
         <v>14</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>45.18</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="19">
         <v>15</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>44.31</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18">
       <c r="A22" s="19">
         <v>16</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>43.44</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18">
       <c r="A23" s="19">
         <v>17</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>42.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="19">
         <v>18</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>41.72</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="19">
         <v>19</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="19">
         <v>20</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>40.01</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="19">
         <v>21</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="19">
         <v>22</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="19">
         <v>23</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>37.479999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:18">
       <c r="A30" s="19">
         <v>24</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>36.64</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:18">
       <c r="A31" s="19">
         <v>25</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>35.81</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:18">
       <c r="A32" s="19">
         <v>26</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>34.99</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18">
       <c r="A33" s="19">
         <v>27</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18">
       <c r="A34" s="19">
         <v>28</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>33.33</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18">
       <c r="A35" s="19">
         <v>29</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>32.51</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18">
       <c r="A36" s="19">
         <v>30</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>31.69</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18">
       <c r="A37" s="19">
         <v>31</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>30.87</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18">
       <c r="A38" s="19">
         <v>32</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>30.05</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18">
       <c r="A39" s="19">
         <v>33</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>29.23</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18">
       <c r="A40" s="19">
         <v>34</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>28.42</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18">
       <c r="A41" s="19">
         <v>35</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>27.61</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18">
       <c r="A42" s="19">
         <v>36</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18">
       <c r="A43" s="19">
         <v>37</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18">
       <c r="A44" s="19">
         <v>38</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18">
       <c r="A45" s="19">
         <v>39</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>24.41</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18">
       <c r="A46" s="19">
         <v>40</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>23.62</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18">
       <c r="A47" s="19">
         <v>41</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>22.83</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18">
       <c r="A48" s="19">
         <v>42</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>22.05</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:18">
       <c r="A49" s="19">
         <v>43</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>21.28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:18">
       <c r="A50" s="19">
         <v>44</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>20.51</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:18">
       <c r="A51" s="19">
         <v>45</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>19.739999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:18">
       <c r="A52" s="19">
         <v>46</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:18">
       <c r="A53" s="19">
         <v>47</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>18.239999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:18">
       <c r="A54" s="19">
         <v>48</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:18">
       <c r="A55" s="19">
         <v>49</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>16.78</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:18">
       <c r="A56" s="19">
         <v>50</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>16.059999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:18">
       <c r="A57" s="19">
         <v>51</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:18">
       <c r="A58" s="19">
         <v>52</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>14.67</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18">
       <c r="A59" s="19">
         <v>53</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>14.01</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:18">
       <c r="A60" s="19">
         <v>54</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:18">
       <c r="A61" s="19">
         <v>55</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18">
       <c r="A62" s="19">
         <v>56</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>12.14</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:18">
       <c r="A63" s="19">
         <v>57</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>11.58</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:18">
       <c r="A64" s="19">
         <v>58</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>11.04</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18">
       <c r="A65" s="19">
         <v>59</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18">
       <c r="A66" s="19">
         <v>60</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>10.050000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18">
       <c r="A67" s="19">
         <v>61</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>9.61</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18">
       <c r="A68" s="19">
         <v>62</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18">
       <c r="A69" s="19">
         <v>63</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18">
       <c r="A70" s="19">
         <v>64</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18">
       <c r="A71" s="19">
         <v>65</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18">
       <c r="A72" s="19">
         <v>66</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18">
       <c r="A73" s="19">
         <v>67</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18">
       <c r="A74" s="19">
         <v>68</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>7.04</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18">
       <c r="A75" s="19">
         <v>69</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18">
       <c r="A76" s="19">
         <v>70</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18">
       <c r="A77" s="19">
         <v>71</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18">
       <c r="A78" s="19">
         <v>72</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18">
       <c r="A79" s="19">
         <v>73</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18">
       <c r="A80" s="19">
         <v>74</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18">
       <c r="A81" s="19">
         <v>75</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18">
       <c r="A82" s="19">
         <v>76</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18">
       <c r="A83" s="19">
         <v>77</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18">
       <c r="A84" s="19">
         <v>78</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18">
       <c r="A85" s="19">
         <v>79</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18">
       <c r="A86" s="19">
         <v>80</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18">
       <c r="A87" s="19">
         <v>81</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18">
       <c r="A88" s="19">
         <v>82</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18">
       <c r="A89" s="19">
         <v>83</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18">
       <c r="A90" s="19">
         <v>84</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18">
       <c r="A91" s="19">
         <v>85</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18">
       <c r="A92" s="19">
         <v>86</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18">
       <c r="A93" s="19">
         <v>87</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18">
       <c r="A94" s="19">
         <v>88</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18">
       <c r="A95" s="19">
         <v>89</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18">
       <c r="A96" s="19">
         <v>90</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18">
       <c r="A97" s="19">
         <v>91</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18">
       <c r="A98" s="19">
         <v>92</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18">
       <c r="A99" s="19">
         <v>93</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18">
       <c r="A100" s="19">
         <v>94</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18">
       <c r="A101" s="19">
         <v>95</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18">
       <c r="A102" s="19">
         <v>96</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18">
       <c r="A103" s="19">
         <v>97</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18">
       <c r="A104" s="19">
         <v>98</v>
       </c>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="R104" s="18"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18">
       <c r="A105" s="19">
         <v>99</v>
       </c>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="R105" s="18"/>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18">
       <c r="A106" s="19">
         <v>100</v>
       </c>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="R106" s="18"/>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:18">
       <c r="A108" s="30" t="s">
         <v>54</v>
       </c>
@@ -6534,9 +6534,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R108"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.47265625" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="9" customWidth="1"/>
@@ -6551,7 +6551,7 @@
     <col min="17" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18">
       <c r="A1" s="43" t="s">
         <v>48</v>
       </c>
@@ -6573,7 +6573,7 @@
       <c r="Q1" s="44"/>
       <c r="R1" s="44"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="45" t="s">
         <v>15</v>
       </c>
@@ -6595,7 +6595,7 @@
       <c r="Q2" s="44"/>
       <c r="R2" s="44"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -6615,7 +6615,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" ht="10.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="10.5" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="46" t="s">
         <v>16</v>
@@ -6639,7 +6639,7 @@
       <c r="Q4" s="46"/>
       <c r="R4" s="46"/>
     </row>
-    <row r="5" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="40.5">
       <c r="A5" s="24" t="s">
         <v>18</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>24.84</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>50.53</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>55.23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>55.42</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18">
       <c r="A11" s="7">
         <v>5</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>55.24</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>54.78</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18">
       <c r="A13" s="7">
         <v>7</v>
       </c>
@@ -7125,7 +7125,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18">
       <c r="A14" s="7">
         <v>8</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>53.53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18">
       <c r="A15" s="7">
         <v>9</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>52.79</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18">
       <c r="A16" s="7">
         <v>10</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="7">
         <v>11</v>
       </c>
@@ -7341,7 +7341,7 @@
         <v>51.17</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="7">
         <v>12</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>50.31</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="7">
         <v>13</v>
       </c>
@@ -7449,7 +7449,7 @@
         <v>49.44</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="7">
         <v>14</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>48.56</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="7">
         <v>15</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>47.68</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18">
       <c r="A22" s="7">
         <v>16</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>46.81</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18">
       <c r="A23" s="7">
         <v>17</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>45.96</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="7">
         <v>18</v>
       </c>
@@ -7719,7 +7719,7 @@
         <v>45.11</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="7">
         <v>20</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>43.42</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="7">
         <v>21</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>42.59</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="7">
         <v>22</v>
       </c>
@@ -7935,7 +7935,7 @@
         <v>41.76</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="7">
         <v>23</v>
       </c>
@@ -7989,7 +7989,7 @@
         <v>40.93</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:18">
       <c r="A30" s="7">
         <v>24</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>40.11</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:18">
       <c r="A31" s="7">
         <v>25</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>39.29</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:18">
       <c r="A32" s="7">
         <v>26</v>
       </c>
@@ -8151,7 +8151,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18">
       <c r="A33" s="7">
         <v>27</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>37.659999999999997</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18">
       <c r="A34" s="7">
         <v>28</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>36.840000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18">
       <c r="A35" s="7">
         <v>29</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>36.03</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18">
       <c r="A36" s="7">
         <v>30</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>35.21</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18">
       <c r="A37" s="7">
         <v>31</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>34.39</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18">
       <c r="A38" s="7">
         <v>32</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>33.57</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18">
       <c r="A39" s="7">
         <v>33</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>32.76</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18">
       <c r="A40" s="7">
         <v>34</v>
       </c>
@@ -8583,7 +8583,7 @@
         <v>31.95</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18">
       <c r="A41" s="7">
         <v>35</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>31.14</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18">
       <c r="A42" s="7">
         <v>36</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>30.34</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18">
       <c r="A43" s="7">
         <v>37</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>29.54</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18">
       <c r="A44" s="7">
         <v>38</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>28.74</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18">
       <c r="A45" s="7">
         <v>39</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>27.95</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18">
       <c r="A46" s="7">
         <v>40</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>27.16</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18">
       <c r="A47" s="7">
         <v>41</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>26.37</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18">
       <c r="A48" s="7">
         <v>42</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>25.58</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:18">
       <c r="A49" s="7">
         <v>43</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>24.79</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:18">
       <c r="A50" s="7">
         <v>44</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>24.01</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:18">
       <c r="A51" s="7">
         <v>45</v>
       </c>
@@ -9177,7 +9177,7 @@
         <v>23.23</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:18">
       <c r="A52" s="7">
         <v>46</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>22.45</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:18">
       <c r="A53" s="7">
         <v>47</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>21.69</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:18">
       <c r="A54" s="7">
         <v>48</v>
       </c>
@@ -9339,7 +9339,7 @@
         <v>20.92</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:18">
       <c r="A55" s="7">
         <v>49</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>20.170000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:18">
       <c r="A56" s="7">
         <v>50</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>19.420000000000002</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:18">
       <c r="A57" s="7">
         <v>51</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>18.68</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:18">
       <c r="A58" s="7">
         <v>52</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>17.95</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18">
       <c r="A59" s="7">
         <v>53</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>17.23</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:18">
       <c r="A60" s="7">
         <v>54</v>
       </c>
@@ -9663,7 +9663,7 @@
         <v>16.53</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:18">
       <c r="A61" s="7">
         <v>55</v>
       </c>
@@ -9717,7 +9717,7 @@
         <v>15.85</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18">
       <c r="A62" s="7">
         <v>56</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>15.19</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:18">
       <c r="A63" s="7">
         <v>57</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>14.54</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:18">
       <c r="A64" s="7">
         <v>58</v>
       </c>
@@ -9879,7 +9879,7 @@
         <v>13.92</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18">
       <c r="A65" s="7">
         <v>59</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>13.32</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18">
       <c r="A66" s="7">
         <v>60</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18">
       <c r="A67" s="7">
         <v>61</v>
       </c>
@@ -10041,7 +10041,7 @@
         <v>12.18</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18">
       <c r="A68" s="7">
         <v>62</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>11.66</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18">
       <c r="A69" s="7">
         <v>63</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>11.15</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18">
       <c r="A70" s="7">
         <v>64</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>10.67</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18">
       <c r="A71" s="7">
         <v>65</v>
       </c>
@@ -10257,7 +10257,7 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18">
       <c r="A72" s="7">
         <v>66</v>
       </c>
@@ -10311,7 +10311,7 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18">
       <c r="A73" s="7">
         <v>67</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18">
       <c r="A74" s="7">
         <v>68</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18">
       <c r="A75" s="7">
         <v>69</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>8.69</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18">
       <c r="A76" s="7">
         <v>70</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18">
       <c r="A77" s="7">
         <v>71</v>
       </c>
@@ -10581,7 +10581,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18">
       <c r="A78" s="7">
         <v>72</v>
       </c>
@@ -10635,7 +10635,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18">
       <c r="A79" s="7">
         <v>73</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>7.76</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18">
       <c r="A80" s="7">
         <v>74</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18">
       <c r="A81" s="7">
         <v>75</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18">
       <c r="A82" s="7">
         <v>76</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18">
       <c r="A83" s="7">
         <v>77</v>
       </c>
@@ -10905,7 +10905,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18">
       <c r="A84" s="7">
         <v>78</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18">
       <c r="A85" s="7">
         <v>79</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18">
       <c r="A86" s="7">
         <v>80</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>6.86</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18">
       <c r="A87" s="7">
         <v>81</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>6.72</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18">
       <c r="A88" s="7">
         <v>82</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18">
       <c r="A89" s="7">
         <v>83</v>
       </c>
@@ -11229,7 +11229,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18">
       <c r="A90" s="7">
         <v>84</v>
       </c>
@@ -11283,7 +11283,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18">
       <c r="A91" s="7">
         <v>85</v>
       </c>
@@ -11337,7 +11337,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18">
       <c r="A92" s="7">
         <v>86</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18">
       <c r="A93" s="7">
         <v>87</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18">
       <c r="A94" s="7">
         <v>88</v>
       </c>
@@ -11499,7 +11499,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18">
       <c r="A95" s="7">
         <v>89</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18">
       <c r="A96" s="7">
         <v>90</v>
       </c>
@@ -11607,7 +11607,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18">
       <c r="A97" s="7">
         <v>91</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18">
       <c r="A98" s="7">
         <v>92</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18">
       <c r="A99" s="7">
         <v>93</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18">
       <c r="A100" s="7">
         <v>94</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18">
       <c r="A101" s="7">
         <v>95</v>
       </c>
@@ -11877,7 +11877,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18">
       <c r="A102" s="7">
         <v>96</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>3.66</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18">
       <c r="A103" s="7">
         <v>97</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18">
       <c r="A104" s="7">
         <v>98</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18">
       <c r="A105" s="7">
         <v>99</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18">
       <c r="A106" s="7">
         <v>100</v>
       </c>
@@ -12147,7 +12147,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:18">
       <c r="A108" s="47" t="s">
         <v>53</v>
       </c>
@@ -12185,7 +12185,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="9" customWidth="1"/>
@@ -12197,7 +12197,7 @@
     <col min="17" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="16.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="16.5">
       <c r="A1" s="49" t="s">
         <v>52</v>
       </c>
@@ -12219,7 +12219,7 @@
       <c r="Q1" s="50"/>
       <c r="R1" s="50"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="51" t="s">
         <v>27</v>
       </c>
@@ -12241,7 +12241,7 @@
       <c r="Q2" s="51"/>
       <c r="R2" s="51"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -12261,7 +12261,7 @@
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="15">
       <c r="A4" s="22"/>
       <c r="B4" s="52" t="s">
         <v>28</v>
@@ -12313,7 +12313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="30.3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="30.4" customHeight="1">
       <c r="A5" s="26" t="s">
         <v>18</v>
       </c>
@@ -12367,7 +12367,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -12475,7 +12475,7 @@
         <v>43.47</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -12583,7 +12583,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18">
       <c r="A11" s="7">
         <v>5</v>
       </c>
@@ -12691,7 +12691,7 @@
         <v>53.17</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -12745,7 +12745,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18">
       <c r="A13" s="7">
         <v>7</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>52.49</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18">
       <c r="A14" s="7">
         <v>8</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18">
       <c r="A15" s="7">
         <v>9</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18">
       <c r="A16" s="7">
         <v>10</v>
       </c>
@@ -12961,7 +12961,7 @@
         <v>50.45</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="7">
         <v>11</v>
       </c>
@@ -13015,7 +13015,7 @@
         <v>49.66</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="7">
         <v>12</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>48.86</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="7">
         <v>13</v>
       </c>
@@ -13123,7 +13123,7 @@
         <v>48.03</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="7">
         <v>14</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>47.19</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="7">
         <v>15</v>
       </c>
@@ -13231,7 +13231,7 @@
         <v>46.35</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18">
       <c r="A22" s="7">
         <v>16</v>
       </c>
@@ -13285,7 +13285,7 @@
         <v>45.52</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18">
       <c r="A23" s="7">
         <v>17</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="7">
         <v>18</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>43.89</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>43.08</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="7">
         <v>20</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>42.27</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="7">
         <v>21</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>41.46</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="7">
         <v>22</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="7">
         <v>23</v>
       </c>
@@ -13663,7 +13663,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:18">
       <c r="A30" s="7">
         <v>24</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>39.049999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:18">
       <c r="A31" s="7">
         <v>25</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:18">
       <c r="A32" s="7">
         <v>26</v>
       </c>
@@ -13825,7 +13825,7 @@
         <v>37.450000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18">
       <c r="A33" s="7">
         <v>27</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>36.65</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18">
       <c r="A34" s="7">
         <v>28</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>35.86</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18">
       <c r="A35" s="7">
         <v>29</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>35.06</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18">
       <c r="A36" s="7">
         <v>30</v>
       </c>
@@ -14041,7 +14041,7 @@
         <v>34.26</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18">
       <c r="A37" s="7">
         <v>31</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>33.450000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18">
       <c r="A38" s="7">
         <v>32</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>32.65</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18">
       <c r="A39" s="7">
         <v>33</v>
       </c>
@@ -14203,7 +14203,7 @@
         <v>31.85</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18">
       <c r="A40" s="7">
         <v>34</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>31.04</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18">
       <c r="A41" s="7">
         <v>35</v>
       </c>
@@ -14311,7 +14311,7 @@
         <v>30.24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18">
       <c r="A42" s="7">
         <v>36</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18">
       <c r="A43" s="7">
         <v>37</v>
       </c>
@@ -14419,7 +14419,7 @@
         <v>28.64</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18">
       <c r="A44" s="7">
         <v>38</v>
       </c>
@@ -14473,7 +14473,7 @@
         <v>27.85</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18">
       <c r="A45" s="7">
         <v>39</v>
       </c>
@@ -14527,7 +14527,7 @@
         <v>27.06</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18">
       <c r="A46" s="7">
         <v>40</v>
       </c>
@@ -14581,7 +14581,7 @@
         <v>26.28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18">
       <c r="A47" s="7">
         <v>41</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18">
       <c r="A48" s="7">
         <v>42</v>
       </c>
@@ -14689,7 +14689,7 @@
         <v>24.71</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:18">
       <c r="A49" s="7">
         <v>43</v>
       </c>
@@ -14743,7 +14743,7 @@
         <v>23.93</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:18">
       <c r="A50" s="7">
         <v>44</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>23.15</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:18">
       <c r="A51" s="7">
         <v>45</v>
       </c>
@@ -14851,7 +14851,7 @@
         <v>22.37</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:18">
       <c r="A52" s="7">
         <v>46</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:18">
       <c r="A53" s="7">
         <v>47</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>20.82</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:18">
       <c r="A54" s="7">
         <v>48</v>
       </c>
@@ -15013,7 +15013,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:18">
       <c r="A55" s="7">
         <v>49</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>19.29</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:18">
       <c r="A56" s="7">
         <v>50</v>
       </c>
@@ -15121,7 +15121,7 @@
         <v>18.53</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:18">
       <c r="A57" s="7">
         <v>51</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:18">
       <c r="A58" s="7">
         <v>52</v>
       </c>
@@ -15229,7 +15229,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18">
       <c r="A59" s="7">
         <v>53</v>
       </c>
@@ -15283,7 +15283,7 @@
         <v>16.309999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:18">
       <c r="A60" s="7">
         <v>54</v>
       </c>
@@ -15337,7 +15337,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:18">
       <c r="A61" s="7">
         <v>55</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18">
       <c r="A62" s="7">
         <v>56</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:18">
       <c r="A63" s="7">
         <v>57</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>13.56</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:18">
       <c r="A64" s="7">
         <v>58</v>
       </c>
@@ -15553,7 +15553,7 @@
         <v>12.91</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18">
       <c r="A65" s="7">
         <v>59</v>
       </c>
@@ -15607,7 +15607,7 @@
         <v>12.28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18">
       <c r="A66" s="7">
         <v>60</v>
       </c>
@@ -15661,7 +15661,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18">
       <c r="A67" s="7">
         <v>61</v>
       </c>
@@ -15715,7 +15715,7 @@
         <v>11.09</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18">
       <c r="A68" s="7">
         <v>62</v>
       </c>
@@ -15769,7 +15769,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18">
       <c r="A69" s="7">
         <v>63</v>
       </c>
@@ -15823,7 +15823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18">
       <c r="A70" s="7">
         <v>64</v>
       </c>
@@ -15877,7 +15877,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18">
       <c r="A71" s="7">
         <v>65</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18">
       <c r="A72" s="7">
         <v>66</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18">
       <c r="A73" s="7">
         <v>67</v>
       </c>
@@ -16039,7 +16039,7 @@
         <v>8.0500000000000007</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18">
       <c r="A74" s="7">
         <v>68</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18">
       <c r="A75" s="7">
         <v>69</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18">
       <c r="A76" s="7">
         <v>70</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18">
       <c r="A77" s="7">
         <v>71</v>
       </c>
@@ -16255,7 +16255,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18">
       <c r="A78" s="7">
         <v>72</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18">
       <c r="A79" s="7">
         <v>73</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18">
       <c r="A80" s="7">
         <v>74</v>
       </c>
@@ -16417,7 +16417,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18">
       <c r="A81" s="7">
         <v>75</v>
       </c>
@@ -16471,7 +16471,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18">
       <c r="A82" s="7">
         <v>76</v>
       </c>
@@ -16525,7 +16525,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18">
       <c r="A83" s="7">
         <v>77</v>
       </c>
@@ -16579,7 +16579,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18">
       <c r="A84" s="7">
         <v>78</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18">
       <c r="A85" s="7">
         <v>79</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18">
       <c r="A86" s="7">
         <v>80</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18">
       <c r="A87" s="7">
         <v>81</v>
       </c>
@@ -16795,7 +16795,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18">
       <c r="A88" s="7">
         <v>82</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18">
       <c r="A89" s="7">
         <v>83</v>
       </c>
@@ -16903,7 +16903,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18">
       <c r="A90" s="7">
         <v>84</v>
       </c>
@@ -16957,7 +16957,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18">
       <c r="A91" s="7">
         <v>85</v>
       </c>
@@ -17011,7 +17011,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18">
       <c r="A92" s="7">
         <v>86</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18">
       <c r="A93" s="7">
         <v>87</v>
       </c>
@@ -17119,7 +17119,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18">
       <c r="A94" s="7">
         <v>88</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18">
       <c r="A95" s="7">
         <v>89</v>
       </c>
@@ -17227,7 +17227,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18">
       <c r="A96" s="7">
         <v>90</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18">
       <c r="A97" s="7">
         <v>91</v>
       </c>
@@ -17335,7 +17335,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18">
       <c r="A98" s="7">
         <v>92</v>
       </c>
@@ -17389,7 +17389,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18">
       <c r="A99" s="7">
         <v>93</v>
       </c>
@@ -17443,7 +17443,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18">
       <c r="A100" s="7">
         <v>94</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18">
       <c r="A101" s="7">
         <v>95</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18">
       <c r="A102" s="7">
         <v>96</v>
       </c>
@@ -17605,7 +17605,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18">
       <c r="A103" s="7">
         <v>97</v>
       </c>
@@ -17659,7 +17659,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18">
       <c r="A104" s="7">
         <v>98</v>
       </c>
@@ -17713,7 +17713,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18">
       <c r="A105" s="7">
         <v>99</v>
       </c>
@@ -17767,7 +17767,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18">
       <c r="A106" s="7">
         <v>100</v>
       </c>
@@ -17835,9 +17835,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:R106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.83984375" customWidth="1"/>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
@@ -17850,7 +17850,7 @@
     <col min="17" max="18" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="15.75">
       <c r="A1" s="53" t="s">
         <v>51</v>
       </c>
@@ -17872,7 +17872,7 @@
       <c r="Q1" s="54"/>
       <c r="R1" s="54"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="51" t="s">
         <v>30</v>
       </c>
@@ -17894,7 +17894,7 @@
       <c r="Q2" s="51"/>
       <c r="R2" s="51"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="15">
       <c r="A4" s="22"/>
       <c r="B4" s="55" t="s">
         <v>28</v>
@@ -17946,7 +17946,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="40.5">
       <c r="A5" s="28" t="s">
         <v>18</v>
       </c>
@@ -18000,7 +18000,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18">
       <c r="A6" s="7">
         <v>0</v>
       </c>
@@ -18054,7 +18054,7 @@
         <v>24.35</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18">
       <c r="A7" s="7">
         <v>1</v>
       </c>
@@ -18108,7 +18108,7 @@
         <v>48.66</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18">
       <c r="A8" s="7">
         <v>2</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>52.65</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18">
       <c r="A9" s="7">
         <v>3</v>
       </c>
@@ -18216,7 +18216,7 @@
         <v>53.86</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18">
       <c r="A10" s="7">
         <v>4</v>
       </c>
@@ -18270,7 +18270,7 @@
         <v>54.13</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18">
       <c r="A11" s="7">
         <v>5</v>
       </c>
@@ -18324,7 +18324,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18">
       <c r="A12" s="7">
         <v>6</v>
       </c>
@@ -18378,7 +18378,7 @@
         <v>53.57</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18">
       <c r="A13" s="7">
         <v>7</v>
       </c>
@@ -18432,7 +18432,7 @@
         <v>52.99</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18">
       <c r="A14" s="7">
         <v>8</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>52.27</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18">
       <c r="A15" s="7">
         <v>9</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>51.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18">
       <c r="A16" s="7">
         <v>10</v>
       </c>
@@ -18594,7 +18594,7 @@
         <v>50.67</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="7">
         <v>11</v>
       </c>
@@ -18648,7 +18648,7 @@
         <v>49.85</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="7">
         <v>12</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>48.98</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="7">
         <v>13</v>
       </c>
@@ -18756,7 +18756,7 @@
         <v>48.1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="7">
         <v>14</v>
       </c>
@@ -18810,7 +18810,7 @@
         <v>47.23</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="7">
         <v>15</v>
       </c>
@@ -18864,7 +18864,7 @@
         <v>46.36</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18">
       <c r="A22" s="7">
         <v>16</v>
       </c>
@@ -18918,7 +18918,7 @@
         <v>45.52</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18">
       <c r="A23" s="7">
         <v>17</v>
       </c>
@@ -18972,7 +18972,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="7">
         <v>18</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>43.88</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="7">
         <v>19</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>43.08</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="7">
         <v>20</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>42.27</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="7">
         <v>21</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>41.46</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="7">
         <v>22</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>40.65</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="7">
         <v>23</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:18">
       <c r="A30" s="7">
         <v>24</v>
       </c>
@@ -19350,7 +19350,7 @@
         <v>39.049999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:18">
       <c r="A31" s="7">
         <v>25</v>
       </c>
@@ -19404,7 +19404,7 @@
         <v>38.25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:18">
       <c r="A32" s="7">
         <v>26</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>37.450000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18">
       <c r="A33" s="7">
         <v>27</v>
       </c>
@@ -19512,7 +19512,7 @@
         <v>36.65</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18">
       <c r="A34" s="7">
         <v>28</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>35.85</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18">
       <c r="A35" s="7">
         <v>29</v>
       </c>
@@ -19620,7 +19620,7 @@
         <v>35.06</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18">
       <c r="A36" s="7">
         <v>30</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>34.25</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18">
       <c r="A37" s="7">
         <v>31</v>
       </c>
@@ -19728,7 +19728,7 @@
         <v>33.450000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18">
       <c r="A38" s="7">
         <v>32</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>32.65</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18">
       <c r="A39" s="7">
         <v>33</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>31.84</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18">
       <c r="A40" s="7">
         <v>34</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>31.04</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18">
       <c r="A41" s="7">
         <v>35</v>
       </c>
@@ -19944,7 +19944,7 @@
         <v>30.24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18">
       <c r="A42" s="7">
         <v>36</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18">
       <c r="A43" s="7">
         <v>37</v>
       </c>
@@ -20052,7 +20052,7 @@
         <v>28.64</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18">
       <c r="A44" s="7">
         <v>38</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>27.85</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18">
       <c r="A45" s="7">
         <v>39</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>27.06</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18">
       <c r="A46" s="7">
         <v>40</v>
       </c>
@@ -20214,7 +20214,7 @@
         <v>26.27</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18">
       <c r="A47" s="7">
         <v>41</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18">
       <c r="A48" s="7">
         <v>42</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>24.71</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:18">
       <c r="A49" s="7">
         <v>43</v>
       </c>
@@ -20376,7 +20376,7 @@
         <v>23.93</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:18">
       <c r="A50" s="7">
         <v>44</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>23.15</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:18">
       <c r="A51" s="7">
         <v>45</v>
       </c>
@@ -20484,7 +20484,7 @@
         <v>22.37</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:18">
       <c r="A52" s="7">
         <v>46</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:18">
       <c r="A53" s="7">
         <v>47</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>20.82</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:18">
       <c r="A54" s="7">
         <v>48</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:18">
       <c r="A55" s="7">
         <v>49</v>
       </c>
@@ -20700,7 +20700,7 @@
         <v>19.28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:18">
       <c r="A56" s="7">
         <v>50</v>
       </c>
@@ -20754,7 +20754,7 @@
         <v>18.53</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:18">
       <c r="A57" s="7">
         <v>51</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:18">
       <c r="A58" s="7">
         <v>52</v>
       </c>
@@ -20862,7 +20862,7 @@
         <v>17.04</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18">
       <c r="A59" s="7">
         <v>53</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>16.309999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:18">
       <c r="A60" s="7">
         <v>54</v>
       </c>
@@ -20970,7 +20970,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:18">
       <c r="A61" s="7">
         <v>55</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18">
       <c r="A62" s="7">
         <v>56</v>
       </c>
@@ -21078,7 +21078,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:18">
       <c r="A63" s="7">
         <v>57</v>
       </c>
@@ -21132,7 +21132,7 @@
         <v>13.55</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:18">
       <c r="A64" s="7">
         <v>58</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>12.91</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18">
       <c r="A65" s="7">
         <v>59</v>
       </c>
@@ -21240,7 +21240,7 @@
         <v>12.28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18">
       <c r="A66" s="7">
         <v>60</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>11.67</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18">
       <c r="A67" s="7">
         <v>61</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>11.09</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18">
       <c r="A68" s="7">
         <v>62</v>
       </c>
@@ -21402,7 +21402,7 @@
         <v>10.53</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18">
       <c r="A69" s="7">
         <v>63</v>
       </c>
@@ -21456,7 +21456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18">
       <c r="A70" s="7">
         <v>64</v>
       </c>
@@ -21510,7 +21510,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18">
       <c r="A71" s="7">
         <v>65</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18">
       <c r="A72" s="7">
         <v>66</v>
       </c>
@@ -21618,7 +21618,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18">
       <c r="A73" s="7">
         <v>67</v>
       </c>
@@ -21672,7 +21672,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18">
       <c r="A74" s="7">
         <v>68</v>
       </c>
@@ -21726,7 +21726,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18">
       <c r="A75" s="7">
         <v>69</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18">
       <c r="A76" s="7">
         <v>70</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18">
       <c r="A77" s="7">
         <v>71</v>
       </c>
@@ -21888,7 +21888,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18">
       <c r="A78" s="7">
         <v>72</v>
       </c>
@@ -21942,7 +21942,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18">
       <c r="A79" s="7">
         <v>73</v>
       </c>
@@ -21996,7 +21996,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18">
       <c r="A80" s="7">
         <v>74</v>
       </c>
@@ -22050,7 +22050,7 @@
         <v>5.55</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18">
       <c r="A81" s="7">
         <v>75</v>
       </c>
@@ -22104,7 +22104,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18">
       <c r="A82" s="7">
         <v>76</v>
       </c>
@@ -22158,7 +22158,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18">
       <c r="A83" s="7">
         <v>77</v>
       </c>
@@ -22212,7 +22212,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18">
       <c r="A84" s="7">
         <v>78</v>
       </c>
@@ -22266,7 +22266,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18">
       <c r="A85" s="7">
         <v>79</v>
       </c>
@@ -22320,7 +22320,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18">
       <c r="A86" s="7">
         <v>80</v>
       </c>
@@ -22374,7 +22374,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18">
       <c r="A87" s="7">
         <v>81</v>
       </c>
@@ -22428,7 +22428,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18">
       <c r="A88" s="7">
         <v>82</v>
       </c>
@@ -22482,7 +22482,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18">
       <c r="A89" s="7">
         <v>83</v>
       </c>
@@ -22536,7 +22536,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18">
       <c r="A90" s="7">
         <v>84</v>
       </c>
@@ -22590,7 +22590,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18">
       <c r="A91" s="7">
         <v>85</v>
       </c>
@@ -22644,7 +22644,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18">
       <c r="A92" s="7">
         <v>86</v>
       </c>
@@ -22698,7 +22698,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18">
       <c r="A93" s="7">
         <v>87</v>
       </c>
@@ -22752,7 +22752,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18">
       <c r="A94" s="7">
         <v>88</v>
       </c>
@@ -22806,7 +22806,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18">
       <c r="A95" s="7">
         <v>89</v>
       </c>
@@ -22860,7 +22860,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18">
       <c r="A96" s="7">
         <v>90</v>
       </c>
@@ -22914,7 +22914,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18">
       <c r="A97" s="7">
         <v>91</v>
       </c>
@@ -22968,7 +22968,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18">
       <c r="A98" s="7">
         <v>92</v>
       </c>
@@ -23022,7 +23022,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18">
       <c r="A99" s="7">
         <v>93</v>
       </c>
@@ -23076,7 +23076,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18">
       <c r="A100" s="7">
         <v>94</v>
       </c>
@@ -23130,7 +23130,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18">
       <c r="A101" s="7">
         <v>95</v>
       </c>
@@ -23184,7 +23184,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18">
       <c r="A102" s="7">
         <v>96</v>
       </c>
@@ -23238,7 +23238,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18">
       <c r="A103" s="7">
         <v>97</v>
       </c>
@@ -23292,7 +23292,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18">
       <c r="A104" s="7">
         <v>98</v>
       </c>
@@ -23346,7 +23346,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18">
       <c r="A105" s="7">
         <v>99</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18">
       <c r="A106" s="7">
         <v>100</v>
       </c>
@@ -23468,14 +23468,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R106"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.47265625" customWidth="1"/>
-    <col min="7" max="7" width="9.5234375" customWidth="1"/>
-    <col min="16" max="16" width="9.7890625" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="15">
       <c r="A1" s="58" t="s">
         <v>49</v>
       </c>
@@ -23497,7 +23497,7 @@
       <c r="Q1" s="58"/>
       <c r="R1" s="58"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="59" t="s">
         <v>32</v>
       </c>
@@ -23519,7 +23519,7 @@
       <c r="Q2" s="59"/>
       <c r="R2" s="59"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18">
       <c r="B4" s="56" t="s">
         <v>16</v>
       </c>
@@ -23541,7 +23541,7 @@
       <c r="Q4" s="57"/>
       <c r="R4" s="57"/>
     </row>
-    <row r="5" spans="1:18" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18" ht="29.45" customHeight="1">
       <c r="A5" s="32" t="s">
         <v>18</v>
       </c>
@@ -23595,7 +23595,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18">
       <c r="A6" s="6">
         <v>0</v>
       </c>
@@ -23648,7 +23648,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>1</v>
       </c>
@@ -23701,7 +23701,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>2</v>
       </c>
@@ -23754,7 +23754,7 @@
         <v>53.44</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>3</v>
       </c>
@@ -23807,7 +23807,7 @@
         <v>54.34</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>4</v>
       </c>
@@ -23860,7 +23860,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>5</v>
       </c>
@@ -23913,7 +23913,7 @@
         <v>54.21</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -23966,7 +23966,7 @@
         <v>53.73</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>7</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>53.11</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>8</v>
       </c>
@@ -24072,7 +24072,7 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>9</v>
       </c>
@@ -24125,7 +24125,7 @@
         <v>51.61</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>10</v>
       </c>
@@ -24178,7 +24178,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>11</v>
       </c>
@@ -24231,7 +24231,7 @@
         <v>49.96</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>12</v>
       </c>
@@ -24284,7 +24284,7 @@
         <v>49.09</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>13</v>
       </c>
@@ -24337,7 +24337,7 @@
         <v>48.22</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>14</v>
       </c>
@@ -24390,7 +24390,7 @@
         <v>47.35</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>15</v>
       </c>
@@ -24443,7 +24443,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>16</v>
       </c>
@@ -24496,7 +24496,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:18">
       <c r="A23" s="6">
         <v>17</v>
       </c>
@@ -24549,7 +24549,7 @@
         <v>44.87</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:18">
       <c r="A24" s="6">
         <v>18</v>
       </c>
@@ -24602,7 +24602,7 @@
         <v>44.09</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:18">
       <c r="A25" s="6">
         <v>19</v>
       </c>
@@ -24655,7 +24655,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:18">
       <c r="A26" s="6">
         <v>20</v>
       </c>
@@ -24708,7 +24708,7 @@
         <v>42.51</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:18">
       <c r="A27" s="6">
         <v>21</v>
       </c>
@@ -24761,7 +24761,7 @@
         <v>41.73</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:18">
       <c r="A28" s="6">
         <v>22</v>
       </c>
@@ -24814,7 +24814,7 @@
         <v>40.96</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:18">
       <c r="A29" s="6">
         <v>23</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>40.18</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:18">
       <c r="A30" s="6">
         <v>24</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>39.4</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:18">
       <c r="A31" s="6">
         <v>25</v>
       </c>
@@ -24973,7 +24973,7 @@
         <v>38.619999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:18">
       <c r="A32" s="6">
         <v>26</v>
       </c>
@@ -25026,7 +25026,7 @@
         <v>37.840000000000003</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:18">
       <c r="A33" s="6">
         <v>27</v>
       </c>
@@ -25079,7 +25079,7 @@
         <v>37.06</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:18">
       <c r="A34" s="6">
         <v>28</v>
       </c>
@@ -25132,7 +25132,7 @@
         <v>36.270000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:18">
       <c r="A35" s="6">
         <v>29</v>
       </c>
@@ -25185,7 +25185,7 @@
         <v>35.49</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:18">
       <c r="A36" s="6">
         <v>30</v>
       </c>
@@ -25238,7 +25238,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:18">
       <c r="A37" s="6">
         <v>31</v>
       </c>
@@ -25291,7 +25291,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:18">
       <c r="A38" s="6">
         <v>32</v>
       </c>
@@ -25344,7 +25344,7 @@
         <v>33.119999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:18">
       <c r="A39" s="6">
         <v>33</v>
       </c>
@@ -25397,7 +25397,7 @@
         <v>32.33</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:18">
       <c r="A40" s="6">
         <v>34</v>
       </c>
@@ -25450,7 +25450,7 @@
         <v>31.55</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:18">
       <c r="A41" s="6">
         <v>35</v>
       </c>
@@ -25503,7 +25503,7 @@
         <v>30.76</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:18">
       <c r="A42" s="6">
         <v>36</v>
       </c>
@@ -25556,7 +25556,7 @@
         <v>29.98</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:18">
       <c r="A43" s="6">
         <v>37</v>
       </c>
@@ -25609,7 +25609,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:18">
       <c r="A44" s="6">
         <v>38</v>
       </c>
@@ -25662,7 +25662,7 @@
         <v>28.42</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:18">
       <c r="A45" s="6">
         <v>39</v>
       </c>
@@ -25715,7 +25715,7 @@
         <v>27.65</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:18">
       <c r="A46" s="6">
         <v>40</v>
       </c>
@@ -25768,7 +25768,7 @@
         <v>26.88</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:18">
       <c r="A47" s="6">
         <v>41</v>
       </c>
@@ -25821,7 +25821,7 @@
         <v>26.11</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:18">
       <c r="A48" s="6">
         <v>42</v>
       </c>
@@ -25874,7 +25874,7 @@
         <v>25.35</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:18">
       <c r="A49" s="6">
         <v>43</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>24.58</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:18">
       <c r="A50" s="6">
         <v>44</v>
       </c>
@@ -25980,7 +25980,7 @@
         <v>23.81</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:18">
       <c r="A51" s="6">
         <v>45</v>
       </c>
@@ -26033,7 +26033,7 @@
         <v>23.04</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:18">
       <c r="A52" s="6">
         <v>46</v>
       </c>
@@ -26086,7 +26086,7 @@
         <v>22.27</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:18">
       <c r="A53" s="6">
         <v>47</v>
       </c>
@@ -26139,7 +26139,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:18">
       <c r="A54" s="6">
         <v>48</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>20.74</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:18">
       <c r="A55" s="6">
         <v>49</v>
       </c>
@@ -26245,7 +26245,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:18">
       <c r="A56" s="6">
         <v>50</v>
       </c>
@@ -26298,7 +26298,7 @@
         <v>19.239999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:18">
       <c r="A57" s="6">
         <v>51</v>
       </c>
@@ -26351,7 +26351,7 @@
         <v>18.510000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:18">
       <c r="A58" s="6">
         <v>52</v>
       </c>
@@ -26404,7 +26404,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18">
       <c r="A59" s="6">
         <v>53</v>
       </c>
@@ -26457,7 +26457,7 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:18">
       <c r="A60" s="6">
         <v>54</v>
       </c>
@@ -26510,7 +26510,7 @@
         <v>16.38</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:18">
       <c r="A61" s="6">
         <v>55</v>
       </c>
@@ -26563,7 +26563,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18">
       <c r="A62" s="6">
         <v>56</v>
       </c>
@@ -26616,7 +26616,7 @@
         <v>15.03</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:18">
       <c r="A63" s="6">
         <v>57</v>
       </c>
@@ -26669,7 +26669,7 @@
         <v>14.38</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:18">
       <c r="A64" s="6">
         <v>58</v>
       </c>
@@ -26722,7 +26722,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:18">
       <c r="A65" s="6">
         <v>59</v>
       </c>
@@ -26775,7 +26775,7 @@
         <v>13.13</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:18">
       <c r="A66" s="6">
         <v>60</v>
       </c>
@@ -26828,7 +26828,7 @@
         <v>12.53</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:18">
       <c r="A67" s="6">
         <v>61</v>
       </c>
@@ -26881,7 +26881,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:18">
       <c r="A68" s="6">
         <v>62</v>
       </c>
@@ -26934,7 +26934,7 @@
         <v>11.38</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:18">
       <c r="A69" s="6">
         <v>63</v>
       </c>
@@ -26987,7 +26987,7 @@
         <v>10.82</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:18">
       <c r="A70" s="6">
         <v>64</v>
       </c>
@@ -27040,7 +27040,7 @@
         <v>10.29</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:18">
       <c r="A71" s="6">
         <v>65</v>
       </c>
@@ -27093,7 +27093,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:18">
       <c r="A72" s="6">
         <v>66</v>
       </c>
@@ -27146,7 +27146,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:18">
       <c r="A73" s="6">
         <v>67</v>
       </c>
@@ -27199,7 +27199,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:18">
       <c r="A74" s="6">
         <v>68</v>
       </c>
@@ -27252,7 +27252,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:18">
       <c r="A75" s="6">
         <v>69</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:18">
       <c r="A76" s="6">
         <v>70</v>
       </c>
@@ -27358,7 +27358,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:18">
       <c r="A77" s="6">
         <v>71</v>
       </c>
@@ -27411,7 +27411,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:18">
       <c r="A78" s="6">
         <v>72</v>
       </c>
@@ -27464,7 +27464,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:18">
       <c r="A79" s="6">
         <v>73</v>
       </c>
@@ -27517,7 +27517,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:18">
       <c r="A80" s="6">
         <v>74</v>
       </c>
@@ -27570,7 +27570,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:18">
       <c r="A81" s="6">
         <v>75</v>
       </c>
@@ -27623,7 +27623,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:18">
       <c r="A82" s="6">
         <v>76</v>
       </c>
@@ -27676,7 +27676,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:18">
       <c r="A83" s="6">
         <v>77</v>
       </c>
@@ -27729,7 +27729,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:18">
       <c r="A84" s="6">
         <v>78</v>
       </c>
@@ -27782,7 +27782,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:18">
       <c r="A85" s="6">
         <v>79</v>
       </c>
@@ -27835,7 +27835,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:18">
       <c r="A86" s="6">
         <v>80</v>
       </c>
@@ -27888,7 +27888,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:18">
       <c r="A87" s="6">
         <v>81</v>
       </c>
@@ -27941,7 +27941,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:18">
       <c r="A88" s="6">
         <v>82</v>
       </c>
@@ -27994,7 +27994,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:18">
       <c r="A89" s="6">
         <v>83</v>
       </c>
@@ -28047,7 +28047,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:18">
       <c r="A90" s="6">
         <v>84</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:18">
       <c r="A91" s="6">
         <v>85</v>
       </c>
@@ -28153,7 +28153,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:18">
       <c r="A92" s="6">
         <v>86</v>
       </c>
@@ -28206,7 +28206,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:18">
       <c r="A93" s="6">
         <v>87</v>
       </c>
@@ -28259,7 +28259,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:18">
       <c r="A94" s="6">
         <v>88</v>
       </c>
@@ -28312,7 +28312,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:18">
       <c r="A95" s="6">
         <v>89</v>
       </c>
@@ -28365,7 +28365,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:18">
       <c r="A96" s="6">
         <v>90</v>
       </c>
@@ -28418,7 +28418,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:18">
       <c r="A97" s="6">
         <v>91</v>
       </c>
@@ -28471,7 +28471,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:18">
       <c r="A98" s="6">
         <v>92</v>
       </c>
@@ -28524,7 +28524,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:18">
       <c r="A99" s="6">
         <v>93</v>
       </c>
@@ -28577,7 +28577,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:18">
       <c r="A100" s="6">
         <v>94</v>
       </c>
@@ -28630,7 +28630,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:18">
       <c r="A101" s="6">
         <v>95</v>
       </c>
@@ -28683,7 +28683,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:18">
       <c r="A102" s="6">
         <v>96</v>
       </c>
@@ -28736,7 +28736,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:18">
       <c r="A103" s="6">
         <v>97</v>
       </c>
@@ -28789,7 +28789,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:18">
       <c r="A104" s="6">
         <v>98</v>
       </c>
@@ -28842,7 +28842,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:18">
       <c r="A105" s="6">
         <v>99</v>
       </c>
@@ -28895,7 +28895,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:18">
       <c r="A106" s="6">
         <v>100</v>
       </c>

--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021DA8FF-8B98-406F-B215-D9FB89655593}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B9EF39-25DC-4572-BB6C-1949BA25536B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16515" yWindow="2145" windowWidth="19695" windowHeight="20295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
   <si>
     <t>Notes</t>
   </si>
@@ -215,6 +215,18 @@
 Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
 Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).
 Техническое замечание: строки возрастов 49–50 отсутствуют на скане между PDF-страницами 159 и 160; соответствующие значения восстановлены по смежным lₓ/Tₓ/Lₓ и табличным тождествам.</t>
+  </si>
+  <si>
+    <t>dx qx px Lx Vx для возраста 100</t>
+  </si>
+  <si>
+    <t>и Vx для возрастов 98 99</t>
+  </si>
+  <si>
+    <t>В таблице №63 (1874-1883 Борткевич) оставлены пустыми значения:</t>
+  </si>
+  <si>
+    <t>В данном файле они заполнены вычисленными значениями</t>
   </si>
 </sst>
 </file>
@@ -748,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -921,6 +933,26 @@
       </c>
       <c r="D17" s="1" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -6389,7 +6421,9 @@
       <c r="H104" s="18">
         <v>4.0199999999999996</v>
       </c>
-      <c r="I104" s="18"/>
+      <c r="I104" s="18">
+        <v>2.44</v>
+      </c>
       <c r="J104" s="18"/>
       <c r="K104" s="16">
         <v>127</v>
@@ -6412,7 +6446,9 @@
       <c r="Q104" s="18">
         <v>4.08</v>
       </c>
-      <c r="R104" s="18"/>
+      <c r="R104" s="18">
+        <v>2.38</v>
+      </c>
     </row>
     <row r="105" spans="1:18">
       <c r="A105" s="19">
@@ -6439,7 +6475,9 @@
       <c r="H105" s="18">
         <v>4.1399999999999997</v>
       </c>
-      <c r="I105" s="18"/>
+      <c r="I105" s="18">
+        <v>2.29</v>
+      </c>
       <c r="J105" s="18"/>
       <c r="K105" s="16">
         <v>96</v>
@@ -6462,7 +6500,9 @@
       <c r="Q105" s="18">
         <v>4.24</v>
       </c>
-      <c r="R105" s="18"/>
+      <c r="R105" s="18">
+        <v>2.19</v>
+      </c>
     </row>
     <row r="106" spans="1:18">
       <c r="A106" s="19">
@@ -6471,32 +6511,52 @@
       <c r="B106" s="16">
         <v>66</v>
       </c>
-      <c r="C106" s="16"/>
-      <c r="D106" s="17"/>
-      <c r="E106" s="17"/>
-      <c r="F106" s="16"/>
+      <c r="C106" s="16">
+        <v>18</v>
+      </c>
+      <c r="D106" s="17">
+        <v>0.27272999999999997</v>
+      </c>
+      <c r="E106" s="17">
+        <v>0.72726999999999997</v>
+      </c>
+      <c r="F106" s="16">
+        <v>57</v>
+      </c>
       <c r="G106" s="16">
         <v>288</v>
       </c>
       <c r="H106" s="18">
         <v>4.3600000000000003</v>
       </c>
-      <c r="I106" s="18"/>
+      <c r="I106" s="18">
+        <v>2.09</v>
+      </c>
       <c r="J106" s="18"/>
       <c r="K106" s="16">
         <v>71</v>
       </c>
-      <c r="L106" s="16"/>
-      <c r="M106" s="17"/>
-      <c r="N106" s="17"/>
-      <c r="O106" s="16"/>
+      <c r="L106" s="16">
+        <v>20</v>
+      </c>
+      <c r="M106" s="17">
+        <v>0.28169</v>
+      </c>
+      <c r="N106" s="17">
+        <v>0.71831</v>
+      </c>
+      <c r="O106" s="16">
+        <v>61</v>
+      </c>
       <c r="P106" s="16">
         <v>324</v>
       </c>
       <c r="Q106" s="18">
         <v>4.5599999999999996</v>
       </c>
-      <c r="R106" s="18"/>
+      <c r="R106" s="18">
+        <v>1.97</v>
+      </c>
     </row>
     <row r="108" spans="1:18">
       <c r="A108" s="30" t="s">

--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B9EF39-25DC-4572-BB6C-1949BA25536B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA61C27-885E-4C3F-B604-81A27F61DD1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16515" yWindow="2145" windowWidth="19695" windowHeight="20295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18555" yWindow="1020" windowWidth="23085" windowHeight="20295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,15 @@
     <sheet name="№65 1896-97 II вариант" sheetId="4" r:id="rId5"/>
     <sheet name="№67 1907-1910 II вариант" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -211,12 +219,6 @@
     <t xml:space="preserve">50 губерний Европейской России. 1874—1883 </t>
   </si>
   <si>
-    <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1896/97 г. и данным о родившихся за 1775—1897 гг.
-Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
-Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).
-Техническое замечание: строки возрастов 49–50 отсутствуют на скане между PDF-страницами 159 и 160; соответствующие значения восстановлены по смежным lₓ/Tₓ/Lₓ и табличным тождествам.</t>
-  </si>
-  <si>
     <t>dx qx px Lx Vx для возраста 100</t>
   </si>
   <si>
@@ -227,6 +229,11 @@
   </si>
   <si>
     <t>В данном файле они заполнены вычисленными значениями</t>
+  </si>
+  <si>
+    <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1896/97 г. и данным о родившихся за 1775—1897 гг.
+Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
+Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).</t>
   </si>
 </sst>
 </file>
@@ -425,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -593,6 +600,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,7 +926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="156.75">
+    <row r="15" spans="1:4" ht="114">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
@@ -918,7 +937,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="114">
@@ -937,22 +956,22 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -20707,110 +20726,114 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="7">
+      <c r="A55" s="60">
         <v>49</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="61">
         <v>34806</v>
       </c>
-      <c r="C55" s="13">
-        <v>682</v>
-      </c>
-      <c r="D55" s="14">
-        <v>1.959E-2</v>
-      </c>
-      <c r="E55" s="14">
-        <v>0.98041</v>
-      </c>
-      <c r="F55" s="13">
+      <c r="C55" s="61">
+        <v>684</v>
+      </c>
+      <c r="D55" s="62">
+        <v>1.9650000000000001E-2</v>
+      </c>
+      <c r="E55" s="62">
+        <f>1-D55</f>
+        <v>0.98035000000000005</v>
+      </c>
+      <c r="F55" s="61">
         <v>34465</v>
       </c>
-      <c r="G55" s="13">
+      <c r="G55" s="61">
         <v>672925</v>
       </c>
-      <c r="H55" s="15">
+      <c r="H55" s="63">
         <v>19.329999999999998</v>
       </c>
-      <c r="I55" s="15">
+      <c r="I55" s="63">
         <v>19.13</v>
       </c>
-      <c r="J55" s="15"/>
-      <c r="K55" s="13">
+      <c r="J55" s="63"/>
+      <c r="K55" s="61">
         <v>37152</v>
       </c>
-      <c r="L55" s="13">
-        <v>616</v>
-      </c>
-      <c r="M55" s="14">
-        <v>1.6580000000000001E-2</v>
-      </c>
-      <c r="N55" s="14">
-        <v>0.98341999999999996</v>
-      </c>
-      <c r="O55" s="13">
+      <c r="L55" s="61">
+        <v>620</v>
+      </c>
+      <c r="M55" s="62">
+        <v>1.669E-2</v>
+      </c>
+      <c r="N55" s="62">
+        <f>1-M55</f>
+        <v>0.98331000000000002</v>
+      </c>
+      <c r="O55" s="61">
         <v>36844</v>
       </c>
-      <c r="P55" s="13">
+      <c r="P55" s="61">
         <v>726807</v>
       </c>
-      <c r="Q55" s="15">
+      <c r="Q55" s="63">
         <v>19.559999999999999</v>
       </c>
-      <c r="R55" s="15">
+      <c r="R55" s="63">
         <v>19.28</v>
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="7">
+      <c r="A56" s="60">
         <v>50</v>
       </c>
-      <c r="B56" s="13">
-        <v>34124</v>
-      </c>
-      <c r="C56" s="13">
-        <v>701</v>
-      </c>
-      <c r="D56" s="14">
-        <v>2.0539999999999999E-2</v>
-      </c>
-      <c r="E56" s="14">
-        <v>0.97946</v>
-      </c>
-      <c r="F56" s="13">
+      <c r="B56" s="61">
+        <v>34122</v>
+      </c>
+      <c r="C56" s="61">
+        <v>699</v>
+      </c>
+      <c r="D56" s="62">
+        <v>2.0490000000000001E-2</v>
+      </c>
+      <c r="E56" s="62">
+        <f>1-D56</f>
+        <v>0.97950999999999999</v>
+      </c>
+      <c r="F56" s="61">
         <v>33774</v>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="61">
         <v>638460</v>
       </c>
-      <c r="H56" s="15">
+      <c r="H56" s="63">
         <v>18.71</v>
       </c>
-      <c r="I56" s="15">
+      <c r="I56" s="63">
         <v>18.440000000000001</v>
       </c>
-      <c r="J56" s="15"/>
-      <c r="K56" s="13">
-        <v>36536</v>
-      </c>
-      <c r="L56" s="13">
-        <v>644</v>
-      </c>
-      <c r="M56" s="14">
-        <v>1.763E-2</v>
-      </c>
-      <c r="N56" s="14">
-        <v>0.98236999999999997</v>
-      </c>
-      <c r="O56" s="13">
+      <c r="J56" s="63"/>
+      <c r="K56" s="61">
+        <v>36532</v>
+      </c>
+      <c r="L56" s="61">
+        <v>640</v>
+      </c>
+      <c r="M56" s="62">
+        <v>1.7520000000000001E-2</v>
+      </c>
+      <c r="N56" s="62">
+        <f>1-M56</f>
+        <v>0.98248000000000002</v>
+      </c>
+      <c r="O56" s="61">
         <v>36214</v>
       </c>
-      <c r="P56" s="13">
+      <c r="P56" s="61">
         <v>689963</v>
       </c>
-      <c r="Q56" s="15">
-        <v>18.88</v>
-      </c>
-      <c r="R56" s="15">
+      <c r="Q56" s="63">
+        <v>18.89</v>
+      </c>
+      <c r="R56" s="63">
         <v>18.53</v>
       </c>
     </row>

--- a/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/Russian-Empire/ru-historical-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\Russian-Empire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA61C27-885E-4C3F-B604-81A27F61DD1A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69742D95-978B-40C6-937A-F538EDB8AD37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18555" yWindow="1020" windowWidth="23085" windowHeight="20295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
   <si>
     <t>Notes</t>
   </si>
@@ -234,6 +234,12 @@
     <t>Примечание. Таблица построена для православного населения 50 губерний б. Европейской России по данным об умерших за 1896/97 г. и данным о родившихся за 1775—1897 гг.
 Получившаяся разность l₀ − Σd′ₓ (где d′ₓ — первоначально найденные числа умерших стационарного населения) для мужчин 14 494, для женщин 12 884, распределена пропорционально на возрастные группы, начиная с 15 лет.
 Note. Table de mortalité pour la population orthodoxe de la Russie d’Europe (ancien territoire), calculée à l’aide des décès enregistrés pendant 1896/97, combinés avec les statistiques des naissances. La différence première obtenue l₀ − Σd′ₓ est distribuée par les groupes d’âge à partir de 15 ans (sexe masculin 14 494, sexe féminin — 12 884).</t>
+  </si>
+  <si>
+    <t>1907-1910 гг. включают два года (1909-1910) апогея 6-й холерной пандемии, смертность в которые была на 11.3% выше, чем в среднем за два предыдущие и два последующие года.</t>
+  </si>
+  <si>
+    <t>Общая смертность населения 50 губерний европейской России в 1907-1910 гг. была на 6.7% выше, чем за четыре года 1907, 1908, 1911 и 1912 в среднем.</t>
   </si>
 </sst>
 </file>
@@ -526,6 +532,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -600,18 +618,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -779,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -789,12 +795,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2"/>
@@ -803,12 +809,12 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="17.45" customHeight="1">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
     </row>
     <row r="4" spans="1:4" ht="28.5">
       <c r="A4" s="2" t="s">
@@ -863,12 +869,12 @@
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
     </row>
     <row r="11" spans="1:4" ht="15">
       <c r="A11" s="3" t="s">
@@ -972,6 +978,16 @@
     <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1003,71 +1019,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
     </row>
     <row r="4" spans="1:18" ht="15">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
       <c r="J4" s="23"/>
-      <c r="K4" s="42" t="s">
+      <c r="K4" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
     </row>
     <row r="5" spans="1:18" ht="26.45" customHeight="1">
       <c r="A5" s="33" t="s">
@@ -6631,48 +6647,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4"/>
@@ -6696,27 +6712,27 @@
     </row>
     <row r="4" spans="1:18" ht="10.5" customHeight="1">
       <c r="A4" s="4"/>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
       <c r="J4" s="21"/>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
     </row>
     <row r="5" spans="1:18" ht="40.5">
       <c r="A5" s="24" t="s">
@@ -12227,26 +12243,26 @@
       </c>
     </row>
     <row r="108" spans="1:18">
-      <c r="A108" s="47" t="s">
+      <c r="A108" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B108" s="48"/>
-      <c r="C108" s="48"/>
-      <c r="D108" s="48"/>
-      <c r="E108" s="48"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="48"/>
-      <c r="H108" s="48"/>
-      <c r="I108" s="48"/>
-      <c r="J108" s="48"/>
-      <c r="K108" s="48"/>
-      <c r="L108" s="48"/>
-      <c r="M108" s="48"/>
-      <c r="N108" s="48"/>
-      <c r="O108" s="48"/>
-      <c r="P108" s="48"/>
-      <c r="Q108" s="48"/>
-      <c r="R108" s="48"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="52"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52"/>
+      <c r="G108" s="52"/>
+      <c r="H108" s="52"/>
+      <c r="I108" s="52"/>
+      <c r="J108" s="52"/>
+      <c r="K108" s="52"/>
+      <c r="L108" s="52"/>
+      <c r="M108" s="52"/>
+      <c r="N108" s="52"/>
+      <c r="O108" s="52"/>
+      <c r="P108" s="52"/>
+      <c r="Q108" s="52"/>
+      <c r="R108" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12277,48 +12293,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16.5">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="50"/>
-      <c r="O1" s="50"/>
-      <c r="P1" s="50"/>
-      <c r="Q1" s="50"/>
-      <c r="R1" s="50"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="5"/>
@@ -12342,53 +12358,53 @@
     </row>
     <row r="4" spans="1:18" ht="15">
       <c r="A4" s="22"/>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="56" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="52" t="s">
+      <c r="L4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="52" t="s">
+      <c r="M4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="52" t="s">
+      <c r="N4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="52" t="s">
+      <c r="O4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="52" t="s">
+      <c r="P4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="52" t="s">
+      <c r="Q4" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="52" t="s">
+      <c r="R4" s="56" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17930,98 +17946,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
     </row>
     <row r="4" spans="1:18" ht="15">
       <c r="A4" s="22"/>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="55" t="s">
+      <c r="G4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="55" t="s">
+      <c r="H4" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="55" t="s">
+      <c r="I4" s="59" t="s">
         <v>28</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="55" t="s">
+      <c r="K4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="M4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="N4" s="55" t="s">
+      <c r="N4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="55" t="s">
+      <c r="O4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="55" t="s">
+      <c r="P4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="55" t="s">
+      <c r="Q4" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="55" t="s">
+      <c r="R4" s="59" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20726,114 +20742,114 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="60">
+      <c r="A55" s="35">
         <v>49</v>
       </c>
-      <c r="B55" s="61">
+      <c r="B55" s="36">
         <v>34806</v>
       </c>
-      <c r="C55" s="61">
+      <c r="C55" s="36">
         <v>684</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="37">
         <v>1.9650000000000001E-2</v>
       </c>
-      <c r="E55" s="62">
+      <c r="E55" s="37">
         <f>1-D55</f>
         <v>0.98035000000000005</v>
       </c>
-      <c r="F55" s="61">
+      <c r="F55" s="36">
         <v>34465</v>
       </c>
-      <c r="G55" s="61">
+      <c r="G55" s="36">
         <v>672925</v>
       </c>
-      <c r="H55" s="63">
+      <c r="H55" s="38">
         <v>19.329999999999998</v>
       </c>
-      <c r="I55" s="63">
+      <c r="I55" s="38">
         <v>19.13</v>
       </c>
-      <c r="J55" s="63"/>
-      <c r="K55" s="61">
+      <c r="J55" s="38"/>
+      <c r="K55" s="36">
         <v>37152</v>
       </c>
-      <c r="L55" s="61">
+      <c r="L55" s="36">
         <v>620</v>
       </c>
-      <c r="M55" s="62">
+      <c r="M55" s="37">
         <v>1.669E-2</v>
       </c>
-      <c r="N55" s="62">
+      <c r="N55" s="37">
         <f>1-M55</f>
         <v>0.98331000000000002</v>
       </c>
-      <c r="O55" s="61">
+      <c r="O55" s="36">
         <v>36844</v>
       </c>
-      <c r="P55" s="61">
+      <c r="P55" s="36">
         <v>726807</v>
       </c>
-      <c r="Q55" s="63">
+      <c r="Q55" s="38">
         <v>19.559999999999999</v>
       </c>
-      <c r="R55" s="63">
+      <c r="R55" s="38">
         <v>19.28</v>
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="60">
+      <c r="A56" s="35">
         <v>50</v>
       </c>
-      <c r="B56" s="61">
+      <c r="B56" s="36">
         <v>34122</v>
       </c>
-      <c r="C56" s="61">
+      <c r="C56" s="36">
         <v>699</v>
       </c>
-      <c r="D56" s="62">
+      <c r="D56" s="37">
         <v>2.0490000000000001E-2</v>
       </c>
-      <c r="E56" s="62">
+      <c r="E56" s="37">
         <f>1-D56</f>
         <v>0.97950999999999999</v>
       </c>
-      <c r="F56" s="61">
+      <c r="F56" s="36">
         <v>33774</v>
       </c>
-      <c r="G56" s="61">
+      <c r="G56" s="36">
         <v>638460</v>
       </c>
-      <c r="H56" s="63">
+      <c r="H56" s="38">
         <v>18.71</v>
       </c>
-      <c r="I56" s="63">
+      <c r="I56" s="38">
         <v>18.440000000000001</v>
       </c>
-      <c r="J56" s="63"/>
-      <c r="K56" s="61">
+      <c r="J56" s="38"/>
+      <c r="K56" s="36">
         <v>36532</v>
       </c>
-      <c r="L56" s="61">
+      <c r="L56" s="36">
         <v>640</v>
       </c>
-      <c r="M56" s="62">
+      <c r="M56" s="37">
         <v>1.7520000000000001E-2</v>
       </c>
-      <c r="N56" s="62">
+      <c r="N56" s="37">
         <f>1-M56</f>
         <v>0.98248000000000002</v>
       </c>
-      <c r="O56" s="61">
+      <c r="O56" s="36">
         <v>36214</v>
       </c>
-      <c r="P56" s="61">
+      <c r="P56" s="36">
         <v>689963</v>
       </c>
-      <c r="Q56" s="63">
+      <c r="Q56" s="38">
         <v>18.89</v>
       </c>
-      <c r="R56" s="63">
+      <c r="R56" s="38">
         <v>18.53</v>
       </c>
     </row>
@@ -23559,70 +23575,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="K4" s="57" t="s">
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="K4" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="57"/>
-      <c r="M4" s="57"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="57"/>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="57"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
     </row>
     <row r="5" spans="1:18" ht="29.45" customHeight="1">
       <c r="A5" s="32" t="s">
